--- a/manufacturing_forms/022_warehouse_divider_curtain_survey--manufacturing_forms.xlsx
+++ b/manufacturing_forms/022_warehouse_divider_curtain_survey--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_james</t>
+          <t>assigned_james_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>assigned_james</t>
+          <t>Assigned James 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>assigned_jim</t>
+          <t>assigned_jim_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>assigned_jim</t>
+          <t>Assigned Jim 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>assigned_james</t>
+          <t>assigned_james_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>assigned_james</t>
+          <t>Assigned James 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assigned_jim</t>
+          <t>assigned_jim_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>assigned_jim</t>
+          <t>Assigned Jim 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'3-pin'}</t>
+          <t>3-pin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '3-Pin'}</t>
+          <t>3-Pin</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'4-pin'}</t>
+          <t>4-pin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '4-Pin'}</t>
+          <t>4-Pin</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'6-pin'}</t>
+          <t>6-pin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '6-Pin'}</t>
+          <t>6-Pin</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_good'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not good'}</t>
+          <t>Not good</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'joe'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1590,63 +1590,63 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>assigned_james_choices</t>
+          <t>assigned_james_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>assigned_james_choices</t>
+          <t>assigned_james_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>assigned_james_choices</t>
+          <t>assigned_james_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1743,63 +1743,63 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>assigned_jim_choices</t>
+          <t>assigned_jim_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>assigned_jim_choices</t>
+          <t>assigned_jim_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>assigned_jim_choices</t>
+          <t>assigned_jim_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1845,114 +1845,114 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>assigned_james_choices</t>
+          <t>assigned_james_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>assigned_james_choices</t>
+          <t>assigned_james_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>assigned_james_choices</t>
+          <t>assigned_james_3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>assigned_jim_choices</t>
+          <t>assigned_jim_3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>assigned_jim_choices</t>
+          <t>assigned_jim_3_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>assigned_jim_choices</t>
+          <t>assigned_jim_3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
